--- a/output/pdf_financials_xlsx/DRT.xlsx
+++ b/output/pdf_financials_xlsx/DRT.xlsx
@@ -5063,13 +5063,13 @@
         <v>6.192</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>6.865</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>10.253</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>12.158</v>
@@ -12106,7 +12106,11 @@
           <t>Translation reserve</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -13038,7 +13042,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -15598,7 +15606,11 @@
           <t>Share‐based payment reserve</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -16998,7 +17010,11 @@
           <t>Share‐based payment reserve</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DRT.xlsx
+++ b/output/pdf_financials_xlsx/DRT.xlsx
@@ -945,40 +945,40 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.291</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.548</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.605</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.399</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.425</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.529</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.238</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>1.587</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1754,37 +1754,37 @@
         <v>-16.495</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>6.591</v>
+        <v>6.882</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>18.183</v>
+        <v>18.731</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>12.136</v>
+        <v>12.741</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-7.267</v>
+        <v>-6.868</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>8.83</v>
+        <v>9.255000000000001</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.377</v>
+        <v>-2.848</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-11.298</v>
+        <v>-11.536</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-53.458</v>
+        <v>-53.535</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-54.942</v>
+        <v>-54.993</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>15.102</v>
+        <v>14.612</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>15.218</v>
+        <v>13.631</v>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
@@ -1854,37 +1854,37 @@
         <v>-16.495</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>6.591</v>
+        <v>6.882</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>18.183</v>
+        <v>18.731</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>12.136</v>
+        <v>12.741</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>5.589</v>
+        <v>5.988</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>22.529</v>
+        <v>22.954</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>8.865</v>
+        <v>9.394</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.408</v>
+        <v>0.17</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-38.945</v>
+        <v>-39.022</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-39.823</v>
+        <v>-39.874</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>24.036</v>
+        <v>23.546</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>21.793</v>
+        <v>20.206</v>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
@@ -1905,37 +1905,37 @@
         <v>-11.7994205801352</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>3.5184087888154</v>
+        <v>3.673750460419903</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>7.684310618066561</v>
+        <v>7.915900686740623</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>4.544807699509419</v>
+        <v>4.771374002921021</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2.467124865917127</v>
+        <v>2.643253479533326</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>8.201877814628606</v>
+        <v>8.356602750099205</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>3.578420489636104</v>
+        <v>3.79195511332674</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.2378911647921076</v>
+        <v>0.09912131866337817</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-26.3867527592772</v>
+        <v>-26.43892325516793</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-23.13125504614866</v>
+        <v>-23.16087848002742</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>13.21160220083438</v>
+        <v>12.94226932188577</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>12.50222301262671</v>
+        <v>11.59179177686116</v>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -40326,7 +40326,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -41074,7 +41074,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -41154,7 +41154,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -45564,7 +45564,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -47106,7 +47106,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -48394,7 +48394,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">

--- a/output/pdf_financials_xlsx/DRT.xlsx
+++ b/output/pdf_financials_xlsx/DRT.xlsx
@@ -2233,7 +2233,7 @@
         <v>59.852</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>22.488</v>
       </c>
       <c r="J37" s="1" t="inlineStr">
         <is>
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>14.063</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0</v>
+        <v>13.93</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>0</v>
@@ -2371,27 +2371,25 @@
         <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>4.734</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.164</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>2.127</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.402</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>0.242</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>3.477</v>
@@ -2422,22 +2420,22 @@
         <v>17.652</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>28.89</v>
+        <v>33.624</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>24.017</v>
+        <v>24.181</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>32.078</v>
+        <v>32.918</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>24.133</v>
+        <v>26.26</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>59.852</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>22.89</v>
       </c>
       <c r="J41" s="1" t="inlineStr">
         <is>
@@ -2445,10 +2443,10 @@
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>3.477</v>
+        <v>17.54</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>7.88</v>
+        <v>21.81</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>0.484</v>
@@ -2788,13 +2786,13 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.549</v>
+        <v>0.422</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>28.281</v>
+        <v>5.391</v>
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
@@ -2802,10 +2800,10 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>21.557</v>
+        <v>7.494</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>21.173</v>
+        <v>7.243</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>21.72</v>
@@ -3621,42 +3619,40 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>11.572</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>5.567</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>12.155</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>10.272</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.62</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>4.921</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>7.82</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>5.562</v>
       </c>
       <c r="M64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>11.243</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>11.114</v>
       </c>
     </row>
     <row r="65">
@@ -3783,33 +3779,31 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>10.801</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>8.714</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.193</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>9.266</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>9.648999999999999</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>8.776</v>
       </c>
       <c r="M67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>2.895</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>5.656</v>
       </c>
     </row>
     <row r="68">
@@ -3825,13 +3819,13 @@
         <v>12.55</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>11.572</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>5.567</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>34.599</v>
@@ -5846,13 +5840,13 @@
         <v>0</v>
       </c>
       <c r="M108" s="3" t="n">
-        <v>0</v>
+        <v>8.715999999999999</v>
       </c>
       <c r="N108" s="3" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="O108" s="3" t="n">
-        <v>0</v>
+        <v>2.948</v>
       </c>
     </row>
     <row r="109">
@@ -6469,7 +6463,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-7.73</v>
       </c>
       <c r="H121" s="3" t="n">
         <v>0</v>
@@ -21652,7 +21646,11 @@
           <t>Impairment charge</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -23390,7 +23388,11 @@
           <t>Deferred income tax (recovery)</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -25114,7 +25116,11 @@
           <t>Proceeds issued on private placement</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -26090,7 +26096,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -26418,7 +26428,11 @@
           <t>Proceeds received on private placement</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -28156,7 +28170,11 @@
           <t>Shares repurchased</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -29090,7 +29108,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -31094,7 +31116,11 @@
           <t>Share repurchased</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -40578,7 +40604,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
           <t>-</t>
